--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E65F817-15D8-46AF-81FC-940CE76A9F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E711CA1-AB77-4326-9D38-92F2E3902252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -365,7 +365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -393,6 +393,17 @@
         <v>475258</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B3" s="3">
+        <v>152142</v>
+      </c>
+      <c r="C3" s="3">
+        <v>476020</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E711CA1-AB77-4326-9D38-92F2E3902252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EA9968-E5A8-4D88-B7C2-F2CE60DE9AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>data</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>alysson</t>
+  </si>
+  <si>
+    <t>17/10/226</t>
   </si>
 </sst>
 </file>
@@ -365,7 +368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -404,6 +407,17 @@
         <v>476020</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B4" s="3">
+        <v>153440</v>
+      </c>
+      <c r="C4" s="3">
+        <v>477288</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EA9968-E5A8-4D88-B7C2-F2CE60DE9AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3BE4E6-2AFC-44E5-9F99-D07D92C7EB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>data</t>
   </si>
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t>alysson</t>
-  </si>
-  <si>
-    <t>17/10/226</t>
   </si>
 </sst>
 </file>
@@ -368,13 +365,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -385,7 +382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>46310</v>
       </c>
@@ -396,7 +393,7 @@
         <v>475258</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46311</v>
       </c>
@@ -407,7 +404,7 @@
         <v>476020</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46312</v>
       </c>
@@ -416,6 +413,17 @@
       </c>
       <c r="C4" s="3">
         <v>477288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B5" s="3">
+        <v>155062</v>
+      </c>
+      <c r="C5" s="3">
+        <v>478562</v>
       </c>
     </row>
   </sheetData>

--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3BE4E6-2AFC-44E5-9F99-D07D92C7EB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C5611E-3A6E-417E-B174-C72A7335DD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,7 +365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -426,6 +426,17 @@
         <v>478562</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B6" s="3">
+        <v>156235</v>
+      </c>
+      <c r="C6" s="3">
+        <v>480673</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C5611E-3A6E-417E-B174-C72A7335DD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2168A6E8-BC50-4F92-8CB9-629FCE516548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -365,13 +365,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,7 +382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46310</v>
       </c>
@@ -393,7 +393,7 @@
         <v>475258</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46311</v>
       </c>
@@ -404,7 +404,7 @@
         <v>476020</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46312</v>
       </c>
@@ -415,7 +415,7 @@
         <v>477288</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46313</v>
       </c>
@@ -426,7 +426,7 @@
         <v>478562</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46314</v>
       </c>
@@ -435,6 +435,17 @@
       </c>
       <c r="C6" s="3">
         <v>480673</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B7" s="3">
+        <v>157535</v>
+      </c>
+      <c r="C7" s="3">
+        <v>482758</v>
       </c>
     </row>
   </sheetData>

--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2168A6E8-BC50-4F92-8CB9-629FCE516548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C7C319-9CDE-46EE-8CFB-D092EFF28CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,7 +365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -448,6 +448,17 @@
         <v>482758</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B8" s="3">
+        <v>159255</v>
+      </c>
+      <c r="C8" s="3">
+        <v>486530</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C7C319-9CDE-46EE-8CFB-D092EFF28CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971FF0E6-12DD-4F2E-AEA4-534434792B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,10 +453,10 @@
         <v>46316</v>
       </c>
       <c r="B8" s="3">
-        <v>159255</v>
+        <v>159370</v>
       </c>
       <c r="C8" s="3">
-        <v>486530</v>
+        <v>486775</v>
       </c>
     </row>
   </sheetData>

--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971FF0E6-12DD-4F2E-AEA4-534434792B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBE51C2-BDBF-4466-8FCD-4F1D571B16A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,7 +365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -459,6 +459,17 @@
         <v>486775</v>
       </c>
     </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B9" s="3">
+        <v>160781</v>
+      </c>
+      <c r="C9" s="3">
+        <v>490976</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBE51C2-BDBF-4466-8FCD-4F1D571B16A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BD8A5D-C1F0-45AE-8C4D-B52D53087F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,7 +365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -470,6 +470,17 @@
         <v>490976</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B10" s="3">
+        <v>162297</v>
+      </c>
+      <c r="C10" s="3">
+        <v>493669</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/seguidores instagram.xlsx
+++ b/data/seguidores instagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BD8A5D-C1F0-45AE-8C4D-B52D53087F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5432C2DA-A7A4-4BFF-A31E-056913616574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -365,13 +365,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,7 +382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>46310</v>
       </c>
@@ -393,7 +393,7 @@
         <v>475258</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46311</v>
       </c>
@@ -404,7 +404,7 @@
         <v>476020</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46312</v>
       </c>
@@ -415,7 +415,7 @@
         <v>477288</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46313</v>
       </c>
@@ -426,7 +426,7 @@
         <v>478562</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>46314</v>
       </c>
@@ -437,7 +437,7 @@
         <v>480673</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>46315</v>
       </c>
@@ -448,7 +448,7 @@
         <v>482758</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>46316</v>
       </c>
@@ -459,7 +459,7 @@
         <v>486775</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>46317</v>
       </c>
@@ -470,7 +470,7 @@
         <v>490976</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46318</v>
       </c>
@@ -479,6 +479,17 @@
       </c>
       <c r="C10" s="3">
         <v>493669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B11" s="3">
+        <v>163896</v>
+      </c>
+      <c r="C11" s="3">
+        <v>494475</v>
       </c>
     </row>
   </sheetData>
